--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/amortisman.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/amortisman.xlsx
@@ -1240,12 +1240,12 @@
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t>₺/m³</t>
+          <t>€/m³</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>₺ / yıl</t>
+          <t>€ / yıl</t>
         </is>
       </c>
     </row>
@@ -1258,17 +1258,17 @@
       <c r="B4" s="20" t="n"/>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>70,00</t>
+          <t>75,71</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.271</t>
         </is>
       </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>14.700</t>
+          <t>15.899</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>23.373</t>
+          <t>25.279</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>₺</t>
+          <t>€</t>
         </is>
       </c>
       <c r="C6" s="22" t="n"/>
@@ -1332,13 +1332,13 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>43.586</t>
+          <t>44.742</t>
         </is>
       </c>
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="E7" s="36" t="n"/>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
     <row r="10" ht="12.6" customHeight="1" thickBot="1">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>⚠️ Not: Bu süreye her yıl güncellenen amortisman tablosundaki işletme giderleri (36 ₺/yıl) dahil edilerek hesaplama yapılmıştır.</t>
+          <t>⚠️ Not: Bu süreye her yıl güncellenen amortisman tablosundaki işletme giderleri (36 €/yıl) dahil edilerek hesaplama yapılmıştır.</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
